--- a/data/trans_dic/P62A$invalidez-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,47 +727,47 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,92</t>
+          <t>0,0; 37,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,53; 82,09</t>
+          <t>31,92; 81,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 64,05</t>
+          <t>13,39; 64,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,85</t>
+          <t>0,0; 59,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 58,76</t>
+          <t>7,27; 58,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 45,21</t>
+          <t>4,38; 43,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,51</t>
+          <t>0,0; 45,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,34</t>
+          <t>0,0; 52,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 65,83</t>
+          <t>15,58; 65,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,44; 52,03</t>
+          <t>21,62; 51,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 44,01</t>
+          <t>10,85; 43,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,88</t>
+          <t>0,0; 42,53</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,01; 79,44</t>
+          <t>38,7; 79,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,39; 69,86</t>
+          <t>38,41; 70,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,07; 70,77</t>
+          <t>33,16; 71,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,79</t>
+          <t>0,0; 31,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,93; 74,62</t>
+          <t>31,16; 74,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,9; 66,08</t>
+          <t>31,83; 64,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 44,47</t>
+          <t>11,77; 44,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 28,03</t>
+          <t>4,8; 28,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,59; 73,16</t>
+          <t>42,28; 73,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,44; 62,82</t>
+          <t>39,49; 63,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,35; 52,91</t>
+          <t>27,26; 52,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 22,85</t>
+          <t>5,36; 23,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,42; 69,03</t>
+          <t>40,68; 71,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,44; 82,14</t>
+          <t>60,42; 82,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,08; 55,39</t>
+          <t>31,59; 54,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 44,99</t>
+          <t>17,39; 47,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,06; 49,47</t>
+          <t>22,51; 50,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,51; 48,45</t>
+          <t>20,36; 49,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 34,59</t>
+          <t>14,35; 35,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,42; 54,09</t>
+          <t>33,67; 53,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,3; 65,2</t>
+          <t>47,42; 66,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,64; 48,42</t>
+          <t>30,86; 48,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,68</t>
+          <t>5,41; 15,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,51; 23,01</t>
+          <t>11,29; 22,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,23; 33,87</t>
+          <t>20,15; 34,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 21,64</t>
+          <t>10,76; 21,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,48</t>
+          <t>1,16; 6,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 27,0</t>
+          <t>10,03; 28,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,26; 36,1</t>
+          <t>17,9; 36,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,73; 27,18</t>
+          <t>11,82; 27,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,35; 40,46</t>
+          <t>26,01; 39,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 21,53</t>
+          <t>11,97; 21,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,84; 31,86</t>
+          <t>21,21; 32,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 21,51</t>
+          <t>12,83; 21,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,53; 18,19</t>
+          <t>11,63; 18,03</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,91</t>
+          <t>0,36; 3,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,03</t>
+          <t>0,3; 1,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,3</t>
+          <t>1,04; 6,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,44; 3,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,23</t>
+          <t>0,43; 4,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 23,15</t>
+          <t>3,0; 23,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,74</t>
+          <t>0,59; 2,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,92</t>
+          <t>0,58; 2,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,08</t>
+          <t>0,34; 2,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,46</t>
+          <t>3,31; 10,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,67</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,83</t>
+          <t>1,1; 5,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,49</t>
+          <t>0,42; 4,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,27; 62,12</t>
+          <t>54,72; 62,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,97</t>
+          <t>0,23; 2,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,96</t>
+          <t>0,61; 2,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,37</t>
+          <t>0,41; 2,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,03; 35,7</t>
+          <t>30,15; 35,58</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,21</t>
+          <t>7,73; 12,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,9; 19,28</t>
+          <t>13,69; 19,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,11</t>
+          <t>7,95; 11,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,26</t>
+          <t>0,81; 2,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,58</t>
+          <t>6,11; 10,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,12</t>
+          <t>8,26; 13,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,26</t>
+          <t>5,48; 9,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,15; 40,27</t>
+          <t>16,01; 40,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,81</t>
+          <t>7,66; 10,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,9; 15,59</t>
+          <t>12,03; 15,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,31</t>
+          <t>7,28; 10,17</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,43; 20,05</t>
+          <t>11,42; 20,11</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 715</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2078,47 +2078,47 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1625</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1535</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 762</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1666</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1408; 3268</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4071</t>
+          <t>0; 5036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2281,57 +2281,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5616; 13751</t>
+          <t>5346; 13623</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1934; 9248</t>
+          <t>1934; 9301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5430</t>
+          <t>0; 4807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>781; 6335</t>
+          <t>784; 6358</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1791; 11002</t>
+          <t>1065; 10630</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4949</t>
+          <t>0; 5868</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6310</t>
+          <t>0; 6314</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2688; 10537</t>
+          <t>2493; 10468</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8809; 21374</t>
+          <t>8884; 21065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2970; 12010</t>
+          <t>2961; 11832</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 8248</t>
+          <t>0; 8583</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9779; 19916</t>
+          <t>9703; 19976</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17937; 32640</t>
+          <t>17944; 32974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10061; 20894</t>
+          <t>9791; 21014</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6516</t>
+          <t>0; 6265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5966; 14391</t>
+          <t>6010; 14455</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12654; 26212</t>
+          <t>12625; 25634</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3350; 12741</t>
+          <t>3373; 12638</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1486; 7246</t>
+          <t>1242; 7350</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18889; 32451</t>
+          <t>18752; 32533</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33213; 54270</t>
+          <t>34117; 54776</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15910; 30781</t>
+          <t>15856; 30350</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2700; 10446</t>
+          <t>2449; 10713</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18970; 31613</t>
+          <t>18629; 32535</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45827; 62284</t>
+          <t>45817; 62669</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24494; 43654</t>
+          <t>24898; 42835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1934</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7168; 18475</t>
+          <t>7141; 19373</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12601; 27027</t>
+          <t>12297; 27776</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9709; 22934</t>
+          <t>9639; 23366</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5815; 13819</t>
+          <t>5732; 14119</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29024; 46977</t>
+          <t>29243; 46529</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61713; 85056</t>
+          <t>61860; 86457</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38657; 61091</t>
+          <t>38927; 61389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5588; 14828</t>
+          <t>5112; 14631</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19437; 38843</t>
+          <t>19065; 38107</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33348; 58736</t>
+          <t>34946; 59470</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22007; 43350</t>
+          <t>21558; 43993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1871; 11032</t>
+          <t>1982; 11372</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7948; 21582</t>
+          <t>8019; 22467</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16528; 34572</t>
+          <t>17140; 35347</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13015; 30166</t>
+          <t>13118; 30102</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27978; 42967</t>
+          <t>27625; 42073</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>30676; 53555</t>
+          <t>29785; 54066</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56094; 85748</t>
+          <t>57083; 88170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37657; 66973</t>
+          <t>39934; 68231</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31875; 50273</t>
+          <t>32151; 49828</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>0; 4723</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1093; 11959</t>
+          <t>1098; 12076</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5336</t>
+          <t>0; 5498</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>955; 6090</t>
+          <t>886; 5803</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1770; 11128</t>
+          <t>1832; 11180</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 8169</t>
+          <t>1000; 8902</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1091; 9905</t>
+          <t>1012; 9428</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14674; 99841</t>
+          <t>12952; 99230</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1894; 12670</t>
+          <t>2707; 12099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3032; 15513</t>
+          <t>3094; 15643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1957; 11618</t>
+          <t>1906; 11412</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21114; 76466</t>
+          <t>24179; 77153</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1825</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5162</t>
+          <t>0; 4667</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6186</t>
+          <t>0; 6360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1062; 9067</t>
+          <t>0; 8786</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3235; 14331</t>
+          <t>3246; 15152</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1258; 13122</t>
+          <t>1231; 11759</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>173136; 198158</t>
+          <t>174562; 199108</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1067; 8924</t>
+          <t>1062; 9082</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4244; 16140</t>
+          <t>3326; 16251</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1794; 12849</t>
+          <t>2219; 12551</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>170044; 202111</t>
+          <t>170683; 201449</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>56950; 90081</t>
+          <t>57073; 90981</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>121069; 167919</t>
+          <t>119227; 166327</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>70139; 109097</t>
+          <t>71692; 106875</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5744; 18124</t>
+          <t>6516; 18862</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>34552; 60976</t>
+          <t>35221; 63012</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>62587; 97897</t>
+          <t>61610; 97220</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39438; 68248</t>
+          <t>40367; 72055</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>142082; 377571</t>
+          <t>150140; 379394</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>101582; 142040</t>
+          <t>100677; 140889</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>192494; 252181</t>
+          <t>194534; 252031</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>119920; 168861</t>
+          <t>119274; 166609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>198735; 348746</t>
+          <t>198670; 349740</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$invalidez-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Edad-trans_dic.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,01</t>
+          <t>0,0; 31,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,92; 81,33</t>
+          <t>34,13; 81,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 64,41</t>
+          <t>13,37; 62,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,18</t>
+          <t>0,0; 66,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 58,98</t>
+          <t>7,3; 59,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 43,68</t>
+          <t>4,47; 43,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,67</t>
+          <t>0,0; 41,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,37</t>
+          <t>0,0; 49,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,58; 65,4</t>
+          <t>15,37; 65,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,62; 51,27</t>
+          <t>22,06; 50,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,85; 43,36</t>
+          <t>10,74; 43,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,53</t>
+          <t>0,0; 39,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,7; 79,69</t>
+          <t>37,7; 78,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,41; 70,57</t>
+          <t>39,86; 70,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,16; 71,17</t>
+          <t>34,38; 70,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,53</t>
+          <t>0,0; 32,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,16; 74,95</t>
+          <t>30,17; 73,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,83; 64,62</t>
+          <t>31,07; 64,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 44,12</t>
+          <t>10,34; 45,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 28,43</t>
+          <t>5,24; 27,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,28; 73,35</t>
+          <t>40,81; 71,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 63,41</t>
+          <t>39,1; 62,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,26; 52,17</t>
+          <t>26,36; 53,01</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,36; 23,43</t>
+          <t>5,71; 24,92</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,68; 71,05</t>
+          <t>39,42; 69,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60,42; 82,65</t>
+          <t>59,9; 81,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 54,35</t>
+          <t>32,89; 54,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 47,18</t>
+          <t>17,54; 45,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,51; 50,84</t>
+          <t>22,96; 48,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,36; 49,36</t>
+          <t>19,7; 48,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,35; 35,34</t>
+          <t>13,1; 33,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,67; 53,57</t>
+          <t>32,76; 54,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,42; 66,27</t>
+          <t>47,21; 66,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,86; 48,66</t>
+          <t>30,51; 48,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 15,48</t>
+          <t>5,76; 15,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 22,57</t>
+          <t>11,14; 22,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,15; 34,29</t>
+          <t>19,92; 34,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,76; 21,96</t>
+          <t>10,62; 21,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,68</t>
+          <t>1,31; 6,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,03; 28,11</t>
+          <t>9,38; 27,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 36,91</t>
+          <t>17,52; 36,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 27,12</t>
+          <t>11,99; 26,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,01; 39,62</t>
+          <t>25,9; 39,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 21,74</t>
+          <t>12,41; 21,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,21; 32,76</t>
+          <t>20,98; 32,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 21,92</t>
+          <t>12,14; 21,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,63; 18,03</t>
+          <t>11,15; 18,05</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,95</t>
+          <t>0,36; 3,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,94</t>
+          <t>0,28; 1,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,33</t>
+          <t>1,04; 6,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,95</t>
+          <t>0,44; 3,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,03</t>
+          <t>0,46; 4,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 23,01</t>
+          <t>17,57; 25,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,62</t>
+          <t>0,48; 2,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,94</t>
+          <t>0,58; 3,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,05</t>
+          <t>0,36; 2,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,56</t>
+          <t>8,05; 11,4</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,43; 3,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,11</t>
+          <t>1,1; 5,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,02</t>
+          <t>0,42; 3,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,72; 62,41</t>
+          <t>54,19; 62,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,0</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,98</t>
+          <t>0,78; 2,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,31</t>
+          <t>0,33; 2,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,15; 35,58</t>
+          <t>29,8; 35,7</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,33</t>
+          <t>7,89; 12,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,09</t>
+          <t>13,92; 19,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,86</t>
+          <t>7,98; 11,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,35</t>
+          <t>0,73; 2,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,94</t>
+          <t>6,18; 10,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,03</t>
+          <t>8,36; 13,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,78</t>
+          <t>5,51; 9,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,01; 40,46</t>
+          <t>36,25; 41,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,72</t>
+          <t>7,56; 10,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,03; 15,58</t>
+          <t>11,99; 15,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,17</t>
+          <t>7,21; 10,02</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,11</t>
+          <t>17,84; 20,89</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3161</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5036</t>
+          <t>0; 4325</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5258</t>
+          <t>0; 4914</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2757</t>
         </is>
       </c>
     </row>
@@ -2281,57 +2281,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5346; 13623</t>
+          <t>5716; 13714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1934; 9301</t>
+          <t>1931; 8969</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4807</t>
+          <t>0; 5592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>784; 6358</t>
+          <t>787; 6407</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1065; 10630</t>
+          <t>1088; 10607</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5868</t>
+          <t>0; 5392</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6314</t>
+          <t>0; 6545</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2493; 10468</t>
+          <t>2460; 10519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8884; 21065</t>
+          <t>9062; 20917</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2961; 11832</t>
+          <t>2930; 11770</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 8583</t>
+          <t>0; 8477</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>6412</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9703; 19976</t>
+          <t>9451; 19708</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17944; 32974</t>
+          <t>18624; 32926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9791; 21014</t>
+          <t>10151; 20862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6265</t>
+          <t>0; 6729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6010; 14455</t>
+          <t>5819; 14228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12625; 25634</t>
+          <t>12323; 25665</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3373; 12638</t>
+          <t>2961; 12905</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1242; 7350</t>
+          <t>1465; 7801</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18752; 32533</t>
+          <t>18101; 31895</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34117; 54776</t>
+          <t>33779; 54044</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15856; 30350</t>
+          <t>15336; 30835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2449; 10713</t>
+          <t>2784; 12152</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>10072</t>
         </is>
       </c>
     </row>
@@ -2692,17 +2692,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18629; 32535</t>
+          <t>18051; 31729</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45817; 62669</t>
+          <t>45423; 62015</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24898; 42835</t>
+          <t>25921; 43293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2712,42 +2712,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7141; 19373</t>
+          <t>7204; 18638</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12297; 27776</t>
+          <t>12547; 26635</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9639; 23366</t>
+          <t>9325; 22830</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5732; 14119</t>
+          <t>5858; 14812</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29243; 46529</t>
+          <t>28451; 47076</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61860; 86457</t>
+          <t>61587; 86505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38927; 61389</t>
+          <t>38494; 61771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5112; 14631</t>
+          <t>6078; 16051</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>37412</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>42838</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19065; 38107</t>
+          <t>18798; 37257</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34946; 59470</t>
+          <t>34549; 59636</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21558; 43993</t>
+          <t>21280; 42417</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1982; 11372</t>
+          <t>2356; 11302</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8019; 22467</t>
+          <t>7500; 21765</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17140; 35347</t>
+          <t>16779; 34528</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13118; 30102</t>
+          <t>13306; 29598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27625; 42073</t>
+          <t>30404; 46141</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29785; 54066</t>
+          <t>30879; 52577</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57083; 88170</t>
+          <t>56480; 87119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39934; 68231</t>
+          <t>37780; 66153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32151; 49828</t>
+          <t>33106; 53605</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>52452</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>55062</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4723</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1098; 12076</t>
+          <t>1093; 11422</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5498</t>
+          <t>0; 5330</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>886; 5803</t>
+          <t>940; 6473</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1832; 11180</t>
+          <t>1844; 11892</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1000; 8902</t>
+          <t>989; 8292</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1012; 9428</t>
+          <t>1079; 9723</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12952; 99230</t>
+          <t>43736; 62705</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2707; 12099</t>
+          <t>2198; 12275</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3094; 15643</t>
+          <t>3095; 16276</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1906; 11412</t>
+          <t>1989; 11534</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24179; 77153</t>
+          <t>46698; 66144</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>186482</t>
+          <t>202546</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>186482</t>
+          <t>202546</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4667</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6360</t>
+          <t>0; 6331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3336,42 +3336,42 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 8786</t>
+          <t>1053; 8877</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3246; 15152</t>
+          <t>3251; 15022</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1231; 11759</t>
+          <t>1237; 10608</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>174562; 199108</t>
+          <t>188928; 217357</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1062; 9082</t>
+          <t>0; 8859</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3326; 16251</t>
+          <t>4243; 15978</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2219; 12551</t>
+          <t>1793; 13275</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>170683; 201449</t>
+          <t>184877; 221463</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>288348</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>299495</t>
+          <t>322848</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>57073; 90981</t>
+          <t>58227; 90227</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>119227; 166327</t>
+          <t>121248; 166025</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>71692; 106875</t>
+          <t>71919; 107131</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6516; 18862</t>
+          <t>6342; 19634</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>35221; 63012</t>
+          <t>35608; 60881</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61610; 97220</t>
+          <t>62373; 98199</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40367; 72055</t>
+          <t>40608; 70976</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>150140; 379394</t>
+          <t>291430; 332244</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100677; 140889</t>
+          <t>99271; 142305</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>194534; 252031</t>
+          <t>193943; 253555</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>119274; 166609</t>
+          <t>118089; 164143</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>198670; 349740</t>
+          <t>299363; 350622</t>
         </is>
       </c>
     </row>
